--- a/estimating/combinations of first layer.xlsx
+++ b/estimating/combinations of first layer.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/steve/python/3d-sudoku/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/steve/python/3d-sudoku/estimating/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583C9584-47E0-ED4D-A4FF-E3CAB7A9BA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81AF70A0-1996-8E48-9BD7-F2AC83C5121E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29600" yWindow="-25780" windowWidth="30240" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29600" yWindow="-25780" windowWidth="30240" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="combinations of first layer" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="32">
   <si>
     <t>Pos</t>
   </si>
@@ -115,6 +115,21 @@
   </si>
   <si>
     <t>Number of solutions found as of:</t>
+  </si>
+  <si>
+    <t>in 24 hours</t>
+  </si>
+  <si>
+    <t>vs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in </t>
+  </si>
+  <si>
+    <t>per hour</t>
+  </si>
+  <si>
+    <t>times faster</t>
   </si>
 </sst>
 </file>
@@ -623,7 +638,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -638,6 +653,8 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1808,14 +1825,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B3B428-EAFB-5246-93AF-14E339590B2B}">
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:J228"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
     <col min="3" max="3" width="26.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -1823,838 +1840,1186 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1507742720</v>
       </c>
       <c r="C2" s="1">
         <f>SUM(A:A)</f>
-        <v>1802287224960</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>2883925238976</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="12">
+        <v>55670784</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2">
+        <f>880132/60/60</f>
+        <v>244.48111111111112</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3015485440</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C3" s="13">
+        <f>C2/24</f>
+        <v>120163551624</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="13">
+        <f>G2/I2</f>
+        <v>227709.9598696559</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>9060120576</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C4" s="13">
+        <f>C3/G3</f>
+        <v>527704.41702586552</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>13107122176</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>18401528832</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>22733276160</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>26625809408</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>29240178688</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>31202620416</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
+        <v>33816989696</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>35779431424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>37741873152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>40356242432</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>42318684160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16">
         <v>1197872128</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>2395744256</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>5316920320</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>9260605440</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>11620632576</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>13374720000</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>15302338560</v>
+        <v>2395744256</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>16724849408</v>
+        <v>5316920320</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>18652467968</v>
+        <v>9260605440</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>20074978816</v>
+        <v>11620632576</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>21497489664</v>
+        <v>13374720000</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>23425108224</v>
+        <v>15302338560</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>24847619072</v>
+        <v>16724849408</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>26775237632</v>
+        <v>18652467968</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>28085941248</v>
+        <v>20074978816</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>29396644864</v>
+        <v>21497489664</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>984482816</v>
+        <v>23425108224</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>1968965632</v>
+        <v>24847619072</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>4890141696</v>
+        <v>26775237632</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>8315629568</v>
+        <v>28085941248</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>9899098112</v>
+        <v>29396644864</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>11322875392</v>
+        <v>32206475264</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>12580496128</v>
+        <v>33517178880</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>14004273408</v>
+        <v>34827882496</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>15261894144</v>
+        <v>35871298048</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>16519514880</v>
+        <v>36891500544</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>17943292160</v>
+        <v>37934916096</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>19200912896</v>
+        <v>984482816</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>20624690176</v>
+        <v>1968965632</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>21642188800</v>
+        <v>4890141696</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>22573712640</v>
+        <v>8315629568</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>23591211264</v>
+        <v>9899098112</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>24522735104</v>
+        <v>11322875392</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>26853128704</v>
+        <v>12580496128</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>1504660992</v>
+        <v>14004273408</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>3009321984</v>
+        <v>15261894144</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>6038397952</v>
+        <v>16519514880</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>8843214848</v>
+        <v>17943292160</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>11444897792</v>
+        <v>19200912896</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>12521877248</v>
+        <v>20624690176</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>13503205120</v>
+        <v>21642188800</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>14580184576</v>
+        <v>22573712640</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>15561512448</v>
+        <v>23591211264</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>16542840320</v>
+        <v>24522735104</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>17619819776</v>
+        <v>26853128704</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>18601147648</v>
+        <v>27870627328</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>19678127104</v>
+        <v>28802151168</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>20899517440</v>
+        <v>29819649792</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>22120907776</v>
+        <v>30751173632</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>23574460928</v>
+        <v>31686958080</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>25028014080</v>
+        <v>32622742528</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>26249404416</v>
+        <v>2067935744</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>27470794752</v>
+        <v>1504660992</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>879710464</v>
+        <v>3009321984</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>1759420928</v>
+        <v>6038397952</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>3351168768</v>
+        <v>8843214848</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>4956625920</v>
+        <v>11444897792</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>6071675136</v>
+        <v>12521877248</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>7152737792</v>
+        <v>13503205120</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>8015625728</v>
+        <v>14580184576</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>8878513664</v>
+        <v>15561512448</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>9621929088</v>
+        <v>16542840320</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>10365344512</v>
+        <v>17619819776</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>11248862848</v>
+        <v>18601147648</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>12132381184</v>
+        <v>19678127104</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>13430728448</v>
+        <v>20899517440</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>14174143872</v>
+        <v>22120907776</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>14917559296</v>
+        <v>23574460928</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>15445194048</v>
+        <v>25028014080</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>16010297216</v>
+        <v>26249404416</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>16537931968</v>
+        <v>27470794752</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>17103035136</v>
+        <v>28587695104</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>626117248</v>
+        <v>29704595456</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>1252234496</v>
+        <v>1110063616</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>3087836416</v>
+        <v>2220127232</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86">
-        <v>4743338752</v>
+        <v>4387482624</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87">
-        <v>5656644352</v>
+        <v>879710464</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88">
-        <v>6457907712</v>
+        <v>1759420928</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89">
-        <v>7240094848</v>
+        <v>3351168768</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90">
-        <v>8022281984</v>
+        <v>4956625920</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91">
-        <v>541352192</v>
+        <v>6071675136</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92">
-        <v>1963863040</v>
+        <v>7152737792</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93">
-        <v>3569172480</v>
+        <v>8015625728</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94">
-        <v>4826793216</v>
+        <v>8878513664</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95">
-        <v>6126177024</v>
+        <v>9621929088</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96">
-        <v>7037326336</v>
+        <v>10365344512</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97">
-        <v>7741202944</v>
+        <v>11248862848</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98">
-        <v>8443325696</v>
+        <v>12132381184</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99">
-        <v>9037990912</v>
+        <v>13430728448</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100">
-        <v>9740113664</v>
+        <v>14174143872</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101">
-        <v>10293179456</v>
+        <v>14917559296</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102">
-        <v>10846245248</v>
+        <v>15445194048</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>11334869888</v>
+        <v>16010297216</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>12318354304</v>
+        <v>16537931968</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>13330060416</v>
+        <v>17103035136</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106">
-        <v>13883126208</v>
+        <v>626117248</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107">
-        <v>14371750848</v>
+        <v>1252234496</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108">
-        <v>14924816640</v>
+        <v>3087836416</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109">
-        <v>15389592128</v>
+        <v>4743338752</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A110">
-        <v>15854367616</v>
+        <v>5656644352</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111">
-        <v>16270033408</v>
+        <v>6457907712</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112">
-        <v>1090379776</v>
+        <v>7240094848</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113">
-        <v>2677415680</v>
+        <v>8022281984</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114">
-        <v>4500838656</v>
+        <v>8696274752</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115">
-        <v>6288519936</v>
+        <v>9218881216</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116">
-        <v>7694057472</v>
+        <v>9892873984</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117">
-        <v>8681640704</v>
+        <v>10415480448</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118">
-        <v>9525231616</v>
+        <v>11483986304</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119">
-        <v>10202741056</v>
+        <v>12579807360</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120">
-        <v>656113152</v>
+        <v>13253800128</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121">
-        <v>1312226304</v>
+        <v>13776406592</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122">
-        <v>2903377152</v>
+        <v>14450399360</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123">
-        <v>4154653952</v>
+        <v>14973005824</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A124">
-        <v>5442208256</v>
+        <v>15545009472</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125">
-        <v>6508537856</v>
+        <v>541352192</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A126">
-        <v>7331020288</v>
+        <v>1963863040</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A127">
-        <v>8005013056</v>
+        <v>3569172480</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A128">
-        <v>8685262336</v>
+        <v>4826793216</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A129">
-        <v>9359255104</v>
+        <v>6126177024</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130">
-        <v>10039504384</v>
+        <v>7037326336</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A131">
-        <v>10719753664</v>
+        <v>7741202944</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A132">
-        <v>11393746432</v>
+        <v>8443325696</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A133">
-        <v>12073995712</v>
+        <v>9037990912</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A134">
-        <v>12747988480</v>
+        <v>9740113664</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A135">
-        <v>14127465728</v>
+        <v>10293179456</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>14873218048</v>
+        <v>10846245248</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A137">
-        <v>15618970368</v>
+        <v>11334869888</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A138">
-        <v>16162622336</v>
+        <v>12318354304</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A139">
-        <v>16684825216</v>
+        <v>13330060416</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A140">
-        <v>17228477184</v>
+        <v>13883126208</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A141">
-        <v>17750680064</v>
+        <v>14371750848</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A142">
-        <v>1022046080</v>
+        <v>14924816640</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A143">
-        <v>2044092160</v>
+        <v>15389592128</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A144">
-        <v>3418686464</v>
+        <v>15854367616</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A145">
-        <v>4854852864</v>
+        <v>16270033408</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A146">
-        <v>6176506880</v>
+        <v>1090379776</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A147">
-        <v>7195574272</v>
+        <v>2677415680</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A148">
-        <v>711393280</v>
+        <v>4500838656</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A149">
-        <v>1422786560</v>
+        <v>6288519936</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A150">
-        <v>3299617280</v>
+        <v>7694057472</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A151">
-        <v>4783716352</v>
+        <v>8681640704</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A152">
-        <v>6215248896</v>
+        <v>9525231616</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A153">
-        <v>1214186496</v>
+        <v>10202741056</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A154">
-        <v>2428372992</v>
+        <v>10880250496</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A155">
-        <v>5616750592</v>
+        <v>11580188416</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A156">
-        <v>656113152</v>
+        <v>12455967232</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A157">
-        <v>1312226304</v>
+        <v>13331746048</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A158">
-        <v>2903377152</v>
+        <v>14668336128</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A159">
-        <v>4154653952</v>
+        <v>16037076736</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A160">
-        <v>5442208256</v>
+        <v>16714586176</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A161">
-        <v>695283968</v>
+        <v>17414524096</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A162">
-        <v>1390567936</v>
+        <v>656113152</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A163">
-        <v>2598255104</v>
+        <v>1312226304</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A164">
-        <v>3804036608</v>
+        <v>2903377152</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A165">
-        <v>4922703360</v>
+        <v>4154653952</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A166">
-        <v>5859466240</v>
+        <v>5442208256</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A167">
+        <v>6508537856</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>7331020288</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>8005013056</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>8685262336</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>9359255104</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>10039504384</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>10719753664</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>11393746432</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>12073995712</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>12747988480</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>14127465728</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>14873218048</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>15618970368</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>16162622336</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>16684825216</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>17228477184</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>17750680064</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>1022046080</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>2044092160</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>3418686464</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>4854852864</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>6176506880</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>7195574272</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>7854195712</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>8512817152</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>9171438592</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>9830060032</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>10640081024</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>11450102016</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>13120835584</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>13922230400</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>14723625216</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>15357342208</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>711393280</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>1422786560</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>3299617280</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>4783716352</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <v>6215248896</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A205">
+        <v>7593050112</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>8682890240</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>1214186496</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A208">
+        <v>2428372992</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A209">
+        <v>5616750592</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <v>8313625600</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A211">
+        <v>656113152</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A212">
+        <v>1312226304</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A213">
+        <v>2903377152</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A214">
+        <v>4154653952</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A215">
+        <v>5442208256</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A216">
+        <v>6508537856</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A217">
+        <v>7331020288</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A218">
+        <v>8005013056</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A219">
+        <v>695283968</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A220">
+        <v>1390567936</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A221">
+        <v>2598255104</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A222">
+        <v>3804036608</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A223">
+        <v>4922703360</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A224">
+        <v>5859466240</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A225">
         <v>6387100992</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A226">
+        <v>6922676288</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A227">
+        <v>7450311040</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A228">
+        <v>7985886336</v>
       </c>
     </row>
   </sheetData>

--- a/estimating/combinations of first layer.xlsx
+++ b/estimating/combinations of first layer.xlsx
@@ -8,14 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/steve/python/3d-sudoku/estimating/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81AF70A0-1996-8E48-9BD7-F2AC83C5121E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56502116-726E-B04B-8FC2-FD1C09D7A317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29600" yWindow="-25780" windowWidth="30240" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29600" yWindow="-25780" windowWidth="30240" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="combinations of first layer" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="C++ speed" sheetId="2" r:id="rId2"/>
+    <sheet name="stop_depth" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">stop_depth!$B$3:$B$14</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">stop_depth!$C$3:$C$14</definedName>
+    <definedName name="_xlchart.v2.2" hidden="1">stop_depth!$B$3:$B$14</definedName>
+    <definedName name="_xlchart.v2.3" hidden="1">stop_depth!$C$3:$C$14</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="59">
   <si>
     <t>Pos</t>
   </si>
@@ -114,22 +121,103 @@
     <t>So update the green cell once level 2 results known</t>
   </si>
   <si>
-    <t>Number of solutions found as of:</t>
-  </si>
-  <si>
-    <t>in 24 hours</t>
-  </si>
-  <si>
-    <t>vs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in </t>
-  </si>
-  <si>
-    <t>per hour</t>
-  </si>
-  <si>
-    <t>times faster</t>
+    <t xml:space="preserve">out-cube8.txt:-- with - 7 - 3 - 5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">out-cube9.txt:-- with - 3 - 5 - 7 </t>
+  </si>
+  <si>
+    <t>out-cube10.txt:-- with - 3 - 5 - 7</t>
+  </si>
+  <si>
+    <t>out-cube11.txt:-- with - 7 - 3 - 5</t>
+  </si>
+  <si>
+    <t>out-cube12.txt:-- with - 7 - 3 - 5</t>
+  </si>
+  <si>
+    <t>out-cube12.txt:-- with - 3 - 5 - 7</t>
+  </si>
+  <si>
+    <t>out-cube12.txt:-- with - 4 - 2 - 2</t>
+  </si>
+  <si>
+    <t>out-cube13.txt:-- with - 3 - 5 - 7</t>
+  </si>
+  <si>
+    <t>out-cube13.txt:-- with - 5 - 7 - 3</t>
+  </si>
+  <si>
+    <t>out-cube13.txt:-- with - 4 - 2 - 2</t>
+  </si>
+  <si>
+    <t>out-cube14.txt:-- with - 3 - 5 - 7</t>
+  </si>
+  <si>
+    <t>out-cube14.txt:-- with - 5 - 7 - 3</t>
+  </si>
+  <si>
+    <t>out-cube14.txt:-- with - 4 - 2 - 2</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>solutions</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Average time</t>
+  </si>
+  <si>
+    <t>solutions per second</t>
+  </si>
+  <si>
+    <t>Comparing workload across the various cube processes</t>
+  </si>
+  <si>
+    <t>stop_depth 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cube #10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cube #11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cube #12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cube #13</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cube #14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cube #15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cube #16</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cube #17</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cube #18</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cube #7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cube #8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cube #9</t>
+  </si>
+  <si>
+    <t>valid variants</t>
   </si>
 </sst>
 </file>
@@ -638,7 +726,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -655,6 +743,8 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -712,6 +802,885 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>stop_depth!$B$3:$B$14</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v> cube #7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> cube #8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> cube #9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> cube #10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v> cube #11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v> cube #12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v> cube #13</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v> cube #14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v> cube #15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v> cube #16</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v> cube #17</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v> cube #18</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>stop_depth!$C$3:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5385612</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6040982</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6233496</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6383600</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8717740</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8717740</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9525790</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11265022</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6823478</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9525790</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10022738</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E5BE-EC44-BADD-06F4BD56A4D2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="475324544"/>
+        <c:axId val="475552080"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="475324544"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="475552080"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="475552080"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="475324544"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A27C08C-6AC7-5195-7B51-F999D290149A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1700,21 +2669,21 @@
       </c>
       <c r="D56" s="1">
         <f t="shared" ref="D56:D58" si="4">C56*D57</f>
-        <v>3672</v>
+        <v>2346</v>
       </c>
       <c r="E56" t="s">
         <v>2</v>
       </c>
       <c r="F56" s="1">
         <f>D56/24</f>
-        <v>153</v>
+        <v>97.75</v>
       </c>
       <c r="G56" t="s">
         <v>3</v>
       </c>
       <c r="H56" s="2">
         <f>F56/365</f>
-        <v>0.41917808219178082</v>
+        <v>0.26780821917808217</v>
       </c>
       <c r="I56" t="s">
         <v>5</v>
@@ -1733,14 +2702,14 @@
       </c>
       <c r="D57" s="1">
         <f t="shared" si="4"/>
-        <v>3672</v>
+        <v>2346</v>
       </c>
       <c r="E57" t="s">
         <v>2</v>
       </c>
       <c r="F57" s="1">
         <f>D57/24</f>
-        <v>153</v>
+        <v>97.75</v>
       </c>
       <c r="G57" t="s">
         <v>3</v>
@@ -1762,14 +2731,14 @@
       </c>
       <c r="D58" s="1">
         <f t="shared" si="4"/>
-        <v>1188</v>
+        <v>759</v>
       </c>
       <c r="E58" t="s">
         <v>2</v>
       </c>
       <c r="F58" s="1">
         <f>D58/24</f>
-        <v>49.5</v>
+        <v>31.625</v>
       </c>
       <c r="G58" t="s">
         <v>3</v>
@@ -1786,19 +2755,17 @@
         <v>20</v>
       </c>
       <c r="C59">
-        <f>18*2</f>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D59" s="10">
-        <f>C59*1</f>
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E59" t="s">
         <v>2</v>
       </c>
       <c r="F59" s="8">
         <f>D59/24</f>
-        <v>1.5</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="G59" t="s">
         <v>3</v>
@@ -1825,1204 +2792,368 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B3B428-EAFB-5246-93AF-14E339590B2B}">
-  <dimension ref="A1:J228"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.5" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14">
+        <v>46023</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="11">
-        <v>46022</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1507742720</v>
+      <c r="B2">
+        <v>121891.048</v>
       </c>
       <c r="C2" s="1">
-        <f>SUM(A:A)</f>
-        <v>2883925238976</v>
-      </c>
-      <c r="D2" t="s">
+        <v>65473163264</v>
+      </c>
+      <c r="G2" s="12"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3">
+        <v>80736.92</v>
+      </c>
+      <c r="C3" s="1">
+        <v>38955118592</v>
+      </c>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="12">
-        <v>55670784</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="B4">
+        <v>72396.94</v>
+      </c>
+      <c r="C4" s="1">
+        <v>32622742528</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>29</v>
       </c>
-      <c r="I2">
-        <f>880132/60/60</f>
-        <v>244.48111111111112</v>
-      </c>
-      <c r="J2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>3015485440</v>
-      </c>
-      <c r="C3" s="13">
-        <f>C2/24</f>
-        <v>120163551624</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B5">
+        <v>64844.250999999997</v>
+      </c>
+      <c r="C5" s="1">
+        <v>29704595456</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="13">
-        <f>G2/I2</f>
-        <v>227709.9598696559</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>9060120576</v>
-      </c>
-      <c r="C4" s="13">
-        <f>C3/G3</f>
-        <v>527704.41702586552</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B6">
+        <v>41221.292000000001</v>
+      </c>
+      <c r="C6" s="1">
+        <v>17103035136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>13107122176</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>18401528832</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>22733276160</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>26625809408</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>29240178688</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>31202620416</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>33816989696</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>35779431424</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>37741873152</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>40356242432</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>42318684160</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>1197872128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2395744256</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>5316920320</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>9260605440</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>11620632576</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>13374720000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>15302338560</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>16724849408</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>18652467968</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>20074978816</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>21497489664</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>23425108224</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>24847619072</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>26775237632</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>28085941248</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>29396644864</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>32206475264</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>33517178880</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>34827882496</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>35871298048</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>36891500544</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>37934916096</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>984482816</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>1968965632</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>4890141696</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>8315629568</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>9899098112</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>11322875392</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>12580496128</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>14004273408</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>15261894144</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>16519514880</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>17943292160</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>19200912896</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>20624690176</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>21642188800</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>22573712640</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>23591211264</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>24522735104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>26853128704</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>27870627328</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>28802151168</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>29819649792</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>30751173632</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>31686958080</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>32622742528</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62">
-        <v>2067935744</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63">
-        <v>1504660992</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64">
-        <v>3009321984</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65">
-        <v>6038397952</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>8843214848</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>11444897792</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <v>12521877248</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>13503205120</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70">
-        <v>14580184576</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>15561512448</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <v>16542840320</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>17619819776</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>18601147648</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A75">
-        <v>19678127104</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A76">
-        <v>20899517440</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A77">
-        <v>22120907776</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A78">
-        <v>23574460928</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>25028014080</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A80">
-        <v>26249404416</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A81">
-        <v>27470794752</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82">
-        <v>28587695104</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A83">
-        <v>29704595456</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A84">
-        <v>1110063616</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85">
-        <v>2220127232</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A86">
-        <v>4387482624</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A87">
-        <v>879710464</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A88">
-        <v>1759420928</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A89">
-        <v>3351168768</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A90">
-        <v>4956625920</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A91">
-        <v>6071675136</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A92">
-        <v>7152737792</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A93">
-        <v>8015625728</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A94">
-        <v>8878513664</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A95">
-        <v>9621929088</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A96">
-        <v>10365344512</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A97">
-        <v>11248862848</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A98">
-        <v>12132381184</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A99">
-        <v>13430728448</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A100">
-        <v>14174143872</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A101">
-        <v>14917559296</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A102">
-        <v>15445194048</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A103">
-        <v>16010297216</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A104">
-        <v>16537931968</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A105">
-        <v>17103035136</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A106">
-        <v>626117248</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A107">
-        <v>1252234496</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A108">
-        <v>3087836416</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A109">
-        <v>4743338752</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A110">
-        <v>5656644352</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A111">
-        <v>6457907712</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A112">
-        <v>7240094848</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A113">
-        <v>8022281984</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A114">
-        <v>8696274752</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A115">
-        <v>9218881216</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A116">
-        <v>9892873984</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A117">
-        <v>10415480448</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A118">
-        <v>11483986304</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A119">
-        <v>12579807360</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A120">
-        <v>13253800128</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A121">
-        <v>13776406592</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A122">
-        <v>14450399360</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A123">
-        <v>14973005824</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A124">
-        <v>15545009472</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A125">
-        <v>541352192</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A126">
-        <v>1963863040</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A127">
-        <v>3569172480</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A128">
-        <v>4826793216</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A129">
-        <v>6126177024</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A130">
-        <v>7037326336</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A131">
-        <v>7741202944</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A132">
-        <v>8443325696</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A133">
-        <v>9037990912</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A134">
-        <v>9740113664</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A135">
-        <v>10293179456</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A136">
-        <v>10846245248</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A137">
-        <v>11334869888</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A138">
-        <v>12318354304</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A139">
-        <v>13330060416</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A140">
-        <v>13883126208</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A141">
-        <v>14371750848</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A142">
-        <v>14924816640</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A143">
-        <v>15389592128</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A144">
-        <v>15854367616</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A145">
+      <c r="B7">
+        <v>83229.520999999993</v>
+      </c>
+      <c r="C7" s="1">
+        <v>34123643648</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>122172.33100000001</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46714152192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9">
+        <v>38352</v>
+      </c>
+      <c r="C9" s="1">
         <v>16270033408</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A146">
-        <v>1090379776</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A147">
-        <v>2677415680</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A148">
-        <v>4500838656</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A149">
-        <v>6288519936</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A150">
-        <v>7694057472</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A151">
-        <v>8681640704</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A152">
-        <v>9525231616</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A153">
-        <v>10202741056</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A154">
-        <v>10880250496</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A155">
-        <v>11580188416</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A156">
-        <v>12455967232</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A157">
-        <v>13331746048</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A158">
-        <v>14668336128</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A159">
-        <v>16037076736</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A160">
-        <v>16714586176</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A161">
-        <v>17414524096</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A162">
-        <v>656113152</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A163">
-        <v>1312226304</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A164">
-        <v>2903377152</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A165">
-        <v>4154653952</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A166">
-        <v>5442208256</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A167">
-        <v>6508537856</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A168">
-        <v>7331020288</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A169">
-        <v>8005013056</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A170">
-        <v>8685262336</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A171">
-        <v>9359255104</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A172">
-        <v>10039504384</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A173">
-        <v>10719753664</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A174">
-        <v>11393746432</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A175">
-        <v>12073995712</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A176">
-        <v>12747988480</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A177">
-        <v>14127465728</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A178">
-        <v>14873218048</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A179">
-        <v>15618970368</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A180">
-        <v>16162622336</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A181">
-        <v>16684825216</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A182">
-        <v>17228477184</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A183">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10">
+        <v>84768.096999999994</v>
+      </c>
+      <c r="C10" s="1">
+        <v>36207573504</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11">
+        <v>121017.13800000001</v>
+      </c>
+      <c r="C11" s="1">
+        <v>48175673600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12">
+        <v>43167.360000000001</v>
+      </c>
+      <c r="C12" s="1">
         <v>17750680064</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A184">
-        <v>1022046080</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A185">
-        <v>2044092160</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A186">
-        <v>3418686464</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A187">
-        <v>4854852864</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A188">
-        <v>6176506880</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A189">
-        <v>7195574272</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A190">
-        <v>7854195712</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A191">
-        <v>8512817152</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A192">
-        <v>9171438592</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A193">
-        <v>9830060032</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A194">
-        <v>10640081024</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A195">
-        <v>11450102016</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A196">
-        <v>13120835584</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A197">
-        <v>13922230400</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A198">
-        <v>14723625216</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A199">
-        <v>15357342208</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A200">
-        <v>711393280</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A201">
-        <v>1422786560</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A202">
-        <v>3299617280</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A203">
-        <v>4783716352</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A204">
-        <v>6215248896</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A205">
-        <v>7593050112</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A206">
-        <v>8682890240</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A207">
-        <v>1214186496</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A208">
-        <v>2428372992</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A209">
-        <v>5616750592</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A210">
-        <v>8313625600</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A211">
-        <v>656113152</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A212">
-        <v>1312226304</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A213">
-        <v>2903377152</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A214">
-        <v>4154653952</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A215">
-        <v>5442208256</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A216">
-        <v>6508537856</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A217">
-        <v>7331020288</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A218">
-        <v>8005013056</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A219">
-        <v>695283968</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A220">
-        <v>1390567936</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A221">
-        <v>2598255104</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A222">
-        <v>3804036608</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A223">
-        <v>4922703360</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A224">
-        <v>5859466240</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A225">
-        <v>6387100992</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A226">
-        <v>6922676288</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A227">
-        <v>7450311040</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A228">
-        <v>7985886336</v>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13">
+        <v>83740.347999999998</v>
+      </c>
+      <c r="C13" s="1">
+        <v>34752132096</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14">
+        <v>121892.86500000001</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46947904512</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16">
+        <f>SUM(B2:B14)</f>
+        <v>1079430.111</v>
+      </c>
+      <c r="C16" s="1">
+        <f>SUM(C2:C14)</f>
+        <v>464800448000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17">
+        <f>B16/13</f>
+        <v>83033.08546153846</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <f>B17/60/60</f>
+        <v>23.06474596153846</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1">
+        <f>C16/B17</f>
+        <v>5597774.0128096165</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D236151-8F1F-BD4A-8426-7CCCBA0A8E1C}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4">
+        <v>5385612</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5">
+        <v>6040982</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6">
+        <v>6233496</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7">
+        <v>6383600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8">
+        <v>8717740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9">
+        <v>8717740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10">
+        <v>9525790</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11">
+        <v>11265022</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12">
+        <v>6823478</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13">
+        <v>9525790</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14">
+        <v>10022738</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/estimating/combinations of first layer.xlsx
+++ b/estimating/combinations of first layer.xlsx
@@ -8,21 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/steve/python/3d-sudoku/estimating/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56502116-726E-B04B-8FC2-FD1C09D7A317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3419C3-9AA2-B34F-8568-B930EBFA0802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29600" yWindow="-25780" windowWidth="30240" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29600" yWindow="-25780" windowWidth="30240" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="combinations of first layer" sheetId="1" r:id="rId1"/>
     <sheet name="C++ speed" sheetId="2" r:id="rId2"/>
     <sheet name="stop_depth" sheetId="3" r:id="rId3"/>
+    <sheet name="total so far" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">stop_depth!$B$3:$B$14</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">stop_depth!$C$3:$C$14</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">stop_depth!$B$3:$B$14</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">stop_depth!$C$3:$C$14</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="60">
   <si>
     <t>Pos</t>
   </si>
@@ -218,6 +213,9 @@
   </si>
   <si>
     <t>valid variants</t>
+  </si>
+  <si>
+    <t>as of 2 Jan 2026</t>
   </si>
 </sst>
 </file>
@@ -3156,4 +3154,210 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4B6FDE1-FBD8-184A-917A-974C5D494967}">
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="49.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1">
+        <v>65473163264</v>
+      </c>
+      <c r="B1" s="13">
+        <f>SUM(A:A)</f>
+        <v>1938254472704</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>117443581952</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>38955118592</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>83165175808</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>32622742528</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>76755557376</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>29704595456</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>61372371968</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>17103035136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>34123643648</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>46714152192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>59128822016</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>71597133568</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>81434407680</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>16270033408</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>36207573504</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>48175673600</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>62087749120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>74271918080</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>84642669696</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>95013421312</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>17750680064</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>34752132096</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>46947904512</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>60759787008</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>74829178624</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>86427203584</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>92843406976</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>22512786432</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>46010959872</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>36602165248</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>17750680064</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>34752132096</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>46947904512</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>13822046720</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>28574774784</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>44708190208</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>